--- a/results/metrics_modelling4_smotenc_mean_opt.xlsx
+++ b/results/metrics_modelling4_smotenc_mean_opt.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH17"/>
+  <dimension ref="A1:DH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7228,6 +7228,6246 @@
       </c>
       <c r="DH17" t="n">
         <v>4.196248604251576e-17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 8, 'sampling_strategy': 0.64}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8858024691358024</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7771836007130125</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.7708333333333333</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8383838383838383</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.9044943820224719</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.8385416666666666</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8702702702702703</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.9137152777777777</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.8279922779922779</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.8383184523809524</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.7394957983193278</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.8380952380952381</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.012358903884887695, 0.019243240356445312, 0.009631872177124023, 0.009219884872436523, 0.009491920471191406, 0.009544134140014648, 0.009647130966186523</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.01130529812404088</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.009631872177124023</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.003389266044186577</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.007426023483276367, 0.007420063018798828, 0.006810188293457031, 0.006429195404052734, 0.00665593147277832, 0.006661891937255859, 0.006766080856323242</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.006881339209420341</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.006766080856323242</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.0003602877848746589</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7735849056603774, 0.8113207547169812, 0.7735849056603774, 0.8490566037735849, 0.7358490566037735, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7611111111111111, 0.818111455108359, 0.7770897832817337, 0.8359133126934984, 0.7476780185758514, 0.686532507739938</t>
+        </is>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.7921761687130993</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.7770897832817337</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.06861040649340025</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.7980433263452131</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.06629828597974184</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.823529411764706, 0.84375, 0.8125, 0.8823529411764706, 0.7741935483870968, 0.782608695652174</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.6842105263157895, 0.761904761904762, 0.7142857142857143, 0.7894736842105263, 0.6818181818181819, 0.5945945945945946</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.731574900747833</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.08837874986841243</v>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7538699690402477, 0.8028273809523809, 0.7633928571428572, 0.8359133126934984, 0.7280058651026393, 0.6886016451233843</t>
+        </is>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.7844868603623159</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.7633928571428572</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.07049487784601152</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.8373988199767985</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.823529411764706</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.05476161868353122</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8484848484848485, 0.9, 0.8666666666666667, 0.8823529411764706, 0.8571428571428571, 0.7714285714285715</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.65, 0.6956521739130435, 0.6521739130434783, 0.7894736842105263, 0.6, 0.6111111111111112</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.6990211034833459</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.09901568629245382</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.866990432536651</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.04877499572481869</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.7941176470588235, 0.7647058823529411, 0.8823529411764706, 0.7058823529411765, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7222222222222222, 0.8421052631578947, 0.7894736842105263, 0.7894736842105263, 0.7894736842105263, 0.5789473684210527</t>
+        </is>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.7723475355054303</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.0930755219513667</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0.8120048019207682</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.0720658168246678</v>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>0.9533834586466166, 0.8587301587301588, 0.9396284829721362, 0.8746130030959752, 0.9365325077399381, 0.8421052631578948, 0.871517027863777</t>
+        </is>
+      </c>
+      <c r="BR18" t="n">
+        <v>0.8966442717437851</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0.8746130030959752</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0.0417249286956199</v>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>0.8113207547169812, 0.8401253918495298, 0.8275862068965517, 0.8244514106583072, 0.8307210031347962, 0.8432601880877743, 0.8338557993730408</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>0.8060004316857328, 0.8425117672229354, 0.8265529684680815, 0.820130595411977, 0.8309777472291433, 0.8486768622733911, 0.8294097431050778</t>
+        </is>
+      </c>
+      <c r="BW18" t="n">
+        <v>0.8291800164851912</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0.8294097431050778</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.01302324152149119</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.8301886792452829</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0.8307210031347962</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0.009849013211805114</v>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>0.8492462311557789, 0.8702290076335879, 0.8614609571788413, 0.86, 0.8636363636363636, 0.8724489795918366, 0.8678304239401496</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>0.7478991596638657, 0.7918367346938776, 0.7717842323651452, 0.7647058823529412, 0.7768595041322314, 0.7967479674796748, 0.7763713080168776</t>
+        </is>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.7751721126720877</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.7763713080168776</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.01517679701328979</v>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>0.7985726954098222, 0.8310328711637327, 0.8166225947719932, 0.8123529411764706, 0.8202479338842975, 0.8345984735357557, 0.8221008659785136</t>
+        </is>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.8193611965600835</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.8202479338842975</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.01111930144672085</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0.8635502804480797</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.007208079504848606</v>
+      </c>
+      <c r="CO18" t="inlineStr">
+        <is>
+          <t>0.8756476683937824, 0.9095744680851063, 0.8952879581151832, 0.8865979381443299, 0.9, 0.9193548387096774, 0.8923076923076924</t>
+        </is>
+      </c>
+      <c r="CP18" t="inlineStr">
+        <is>
+          <t>0.712, 0.7404580152671756, 0.7265625, 0.728, 0.7286821705426356, 0.7368421052631579, 0.7419354838709677</t>
+        </is>
+      </c>
+      <c r="CQ18" t="n">
+        <v>0.7306400392777054</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0.7286821705426356</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0.009541831149390874</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0.8969672233936816</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0.8952879581151832</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0.01339468090583145</v>
+      </c>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>0.824390243902439, 0.8341463414634146, 0.8300970873786407, 0.8349514563106796, 0.8300970873786407, 0.8300970873786407, 0.8446601941747572</t>
+        </is>
+      </c>
+      <c r="CX18" t="inlineStr">
+        <is>
+          <t>0.7876106194690266, 0.8508771929824561, 0.8230088495575221, 0.8053097345132744, 0.831858407079646, 0.8672566371681416, 0.8141592920353983</t>
+        </is>
+      </c>
+      <c r="CY18" t="n">
+        <v>0.8257258189722093</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0.8230088495575221</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0.02508773325040542</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0.8326342139981733</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0.8300970873786407</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0.005849962368665048</v>
+      </c>
+      <c r="DE18" t="inlineStr">
+        <is>
+          <t>0.9004748543060651, 0.914548566538297, 0.9048672566371682, 0.9136308961250967, 0.9032777730045536, 0.9171320560185583, 0.9102371337743793</t>
+        </is>
+      </c>
+      <c r="DF18" t="n">
+        <v>0.909166933772017</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0.9102371337743793</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0.005882165721418422</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 9, 'sampling_strategy': 0.64}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7083333333333333</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9527272727272728</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7855392156862745</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.9361702127659575</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8383838383838383</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6422018348623854</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8860759493670886</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.7446808510638299</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.9425153872953199</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.8132271250393042</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.8535884333991406</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.9521276595744681</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.8211009174311926</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8817733990147784</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0.012748956680297852, 0.009263277053833008, 0.009882211685180664, 0.008867025375366211, 0.009155988693237305, 0.008667945861816406, 0.009546041488647461</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.00973306383405413</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.009263277053833008</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.001286803700366075</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0.006842851638793945, 0.006551980972290039, 0.0063059329986572266, 0.006299018859863281, 0.0059909820556640625, 0.0057010650634765625, 0.006259918212890625</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.006278821400233677</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.006299018859863281</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.000340357048112279</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.6981132075471698, 0.8490566037735849, 0.8113207547169812, 0.8490566037735849, 0.8679245283018868, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>0.8692307692307693, 0.7032967032967032, 0.8745421245421245, 0.848901098901099, 0.8745421245421245, 0.8644688644688645, 0.9102564102564102</t>
+        </is>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.8493197278911566</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.8692307692307693</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.06203047950292868</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.8305380852550664</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.05728827886861324</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>0.7878787878787877, 0.5555555555555556, 0.7647058823529412, 0.7222222222222223, 0.7647058823529412, 0.7741935483870968, 0.8</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>0.9066666666666667, 0.7714285714285716, 0.8888888888888888, 0.8571428571428572, 0.8888888888888888, 0.9066666666666667, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.874441570055252</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.0449324886478329</v>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>0.8472727272727272, 0.6634920634920636, 0.826797385620915, 0.7896825396825398, 0.826797385620915, 0.8404301075268817, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.8064537763668793</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.826797385620915</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.06132551399881045</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.7384659826785064</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.7647058823529412</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.07801251578236361</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>0.7222222222222222, 0.45454545454545453, 0.65, 0.5909090909090909, 0.65, 0.7058823529411765, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8709677419354839, 0.9696969696969697, 0.967741935483871, 0.9696969696969697, 0.9444444444444444, 1.0</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.9524275008145976</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.03752578997665554</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.6343179696120872</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.08331471904527965</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7142857142857143, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.6923076923076923, 0.8205128205128205, 0.7692307692307693, 0.8205128205128205, 0.8717948717948718, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.05791717326315713</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.8891156462585034</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.08371493911790563</v>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>0.9504273504273504, 0.8974358974358976, 0.9725274725274725, 0.9340659340659341, 0.8956043956043956, 0.9450549450549451, 0.9963369963369964</t>
+        </is>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.9416361416361417</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0.9450549450549451</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0.03415369185402355</v>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>0.8238993710691824, 0.8463949843260188, 0.8244514106583072, 0.8307210031347962, 0.8495297805642633, 0.8244514106583072, 0.8213166144200627</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>0.8421855921855922, 0.8653343388637507, 0.842885872297637, 0.8434137757667169, 0.8562342885872298, 0.8466314731020614, 0.8332579185520361</t>
+        </is>
+      </c>
+      <c r="BW19" t="n">
+        <v>0.847134751336432</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0.8434137757667169</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0.009733881548690303</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0.8315377964044197</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0.8244514106583072</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>0.01074620535575119</v>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>0.7254901960784315, 0.7586206896551725, 0.7281553398058254, 0.7326732673267328, 0.7551020408163265, 0.7307692307692307, 0.7192118226600985</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.8873563218390804, 0.8703703703703703, 0.8761467889908258, 0.8914027149321265, 0.8697674418604652, 0.8689655172413794</t>
+        </is>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.8763399322292312</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0.008595152543608407</v>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>0.7979302832244008, 0.8229885057471265, 0.7992628550880978, 0.8044100281587793, 0.8232523778742264, 0.800268336314848, 0.794088669950739</t>
+        </is>
+      </c>
+      <c r="CI19" t="n">
+        <v>0.8060287223368883</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0.800268336314848</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.01117405993506608</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0.7357175124445455</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0.01398106186823619</v>
+      </c>
+      <c r="CO19" t="inlineStr">
+        <is>
+          <t>0.6166666666666667, 0.652542372881356, 0.6198347107438017, 0.6324786324786325, 0.6666666666666666, 0.6178861788617886, 0.6186440677966102</t>
+        </is>
+      </c>
+      <c r="CP19" t="inlineStr">
+        <is>
+          <t>0.9494949494949495, 0.9601990049751243, 0.9494949494949495, 0.9455445544554455, 0.9471153846153846, 0.9540816326530612, 0.9402985074626866</t>
+        </is>
+      </c>
+      <c r="CQ19" t="n">
+        <v>0.9494612833073716</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>0.9494949494949495</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>0.005873050172090341</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>0.6321027565850745</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0.6198347107438017</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0.0184569316593858</v>
+      </c>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9058823529411765, 0.8823529411764706, 0.8705882352941177, 0.8705882352941177, 0.8941176470588236, 0.8588235294117647</t>
+        </is>
+      </c>
+      <c r="CX19" t="inlineStr">
+        <is>
+          <t>0.8034188034188035, 0.8247863247863247, 0.8034188034188035, 0.8162393162393162, 0.8418803418803419, 0.7991452991452992, 0.8076923076923077</t>
+        </is>
+      </c>
+      <c r="CY19" t="n">
+        <v>0.8137973137973137</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0.01405477952774276</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0.8804721888755502</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>0.01463699966279366</v>
+      </c>
+      <c r="DE19" t="inlineStr">
+        <is>
+          <t>0.9426129426129426, 0.9525389643036702, 0.9397687280040221, 0.9486173956762193, 0.9451483157365511, 0.9491704374057316, 0.934238310708899</t>
+        </is>
+      </c>
+      <c r="DF19" t="n">
+        <v>0.9445850134925766</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0.9451483157365511</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0.00579419400800713</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 9, 'sampling_strategy': 0.73}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8834876543209876</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8366013071895425</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8287037037037037</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.7843137254901961</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.898989898989899</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.9402173913043478</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.9010416666666666</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9202127659574467</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9740823412698413</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.8912990435291821</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.898139880952381</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.831858407079646</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.8952380952380953</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.8623853211009175</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>0.00992894172668457, 0.008590221405029297, 0.009478092193603516, 0.008577108383178711, 0.00857996940612793, 0.008736848831176758, 0.008983850479125977</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.008982147489275252</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.008736848831176758</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.0004901843316733005</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>0.00975489616394043, 0.00806570053100586, 0.007862091064453125, 0.008146047592163086, 0.008098125457763672, 0.007826089859008789, 0.007757902145385742</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.008215836116245814</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.008065700531005859</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.0006432855386823398</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7735849056603774, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887, 0.8867924528301887, 0.8301886792452831</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>0.8804511278195488, 0.7746031746031746, 0.8707430340557275, 0.8707430340557275, 0.8769349845201238, 0.9001547987616099, 0.8095975232198143</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.8547468110051037</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.8707430340557275</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.04172722859911419</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.8546970150743737</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.04154529543137372</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>0.9315068493150684, 0.8181818181818182, 0.8709677419354839, 0.8709677419354839, 0.9117647058823528, 0.90625, 0.8695652173913043</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>0.8571428571428572, 0.7000000000000001, 0.8181818181818181, 0.8181818181818181, 0.8421052631578947, 0.8571428571428571, 0.7567567567567567</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.8070730529377146</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.0540956877030524</v>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>0.8943248532289628, 0.7590909090909091, 0.8445747800586509, 0.8445747800586509, 0.8769349845201238, 0.8816964285714286, 0.8131609870740305</t>
+        </is>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.8449082460861082</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.8445747800586509</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.04341462819589689</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.8827434392345017</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.03462423803639846</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8709677419354839, 0.9642857142857143, 0.9642857142857143, 0.9117647058823529, 0.9666666666666667, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>0.9375, 0.6363636363636364, 0.72, 0.72, 0.8421052631578947, 0.782608695652174, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.7737650532787832</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0.08962966689254877</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0.9185500346148646</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0.04333711691104342</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.7714285714285715, 0.7941176470588235, 0.7941176470588235, 0.9117647058823529, 0.8529411764705882, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.7777777777777778, 0.9473684210526315, 0.9473684210526315, 0.8421052631578947, 0.9473684210526315, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.8554720133667502</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.08449746237921658</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0.8540216086434574</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0.06752890486872815</v>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>0.9300751879699248, 0.8563492063492064, 0.9373065015479877, 0.9566563467492261, 0.8653250773993808, 0.931888544891641, 0.914860681114551</t>
+        </is>
+      </c>
+      <c r="BR20" t="n">
+        <v>0.9132087922888454</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0.9300751879699248</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0.03511285772280473</v>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>0.889937106918239, 0.896551724137931, 0.8996865203761756, 0.9028213166144201, 0.8934169278996865, 0.8934169278996865, 0.8871473354231975</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>0.8888193395208288, 0.892255027813436, 0.8983589655468682, 0.9047813386029728, 0.891507002319787, 0.8974997852049145, 0.8826574447976631</t>
+        </is>
+      </c>
+      <c r="BW20" t="n">
+        <v>0.8936969862580671</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0.892255027813436</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0.006671864001489605</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0.8947111227527621</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0.8934169278996865</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>0.005032318778717706</v>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>0.9127182044887782, 0.9185185185185186, 0.9207920792079209, 0.9226932668329177, 0.9158415841584159, 0.9145728643216081, 0.9113300492610837</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>0.851063829787234, 0.8583690987124464, 0.8632478632478632, 0.8691983122362869, 0.8547008547008548, 0.8583333333333333, 0.8448275862068965</t>
+        </is>
+      </c>
+      <c r="CE20" t="n">
+        <v>0.8571058397464164</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0.8583333333333333</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0.007368855839940176</v>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>0.8818910171380061, 0.8884438086154824, 0.892019971227892, 0.8959457895346024, 0.8852712194296353, 0.8864530988274707, 0.8780788177339901</t>
+        </is>
+      </c>
+      <c r="CI20" t="n">
+        <v>0.8868719603581542</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0.8864530988274707</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0.005557158418983047</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>0.9166380809698919</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>0.9158415841584159</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>0.003889494675139382</v>
+      </c>
+      <c r="CO20" t="inlineStr">
+        <is>
+          <t>0.9336734693877551, 0.93, 0.9393939393939394, 0.9487179487179487, 0.9343434343434344, 0.9479166666666666, 0.925</t>
+        </is>
+      </c>
+      <c r="CP20" t="inlineStr">
+        <is>
+          <t>0.819672131147541, 0.8403361344537815, 0.8347107438016529, 0.8306451612903226, 0.8264462809917356, 0.8110236220472441, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="CQ20" t="n">
+        <v>0.8266233550709977</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>0.8264462809917356</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>0.009030868689476352</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>0.9370064940728206</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>0.9343434343434344</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>0.008223118376872545</v>
+      </c>
+      <c r="CW20" t="inlineStr">
+        <is>
+          <t>0.8926829268292683, 0.9073170731707317, 0.9029126213592233, 0.8980582524271845, 0.8980582524271845, 0.883495145631068, 0.8980582524271845</t>
+        </is>
+      </c>
+      <c r="CX20" t="inlineStr">
+        <is>
+          <t>0.8849557522123894, 0.8771929824561403, 0.8938053097345132, 0.911504424778761, 0.8849557522123894, 0.911504424778761, 0.8672566371681416</t>
+        </is>
+      </c>
+      <c r="CY20" t="n">
+        <v>0.8901678976201566</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>0.8849557522123894</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0.01545191965783956</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>0.8972260748959779</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>0.8980582524271845</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>0.007024662961148034</v>
+      </c>
+      <c r="DE20" t="inlineStr">
+        <is>
+          <t>0.9702568530110081, 0.9734916559691913, 0.9742890282670332, 0.9738164790789587, 0.9700146060658132, 0.9725921470916745, 0.9657401838645933</t>
+        </is>
+      </c>
+      <c r="DF20" t="n">
+        <v>0.9714572790497532</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>0.9725921470916745</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>0.002808628254391222</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 4, 'sampling_strategy': 0.63}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.761904761904762</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8346560846560847</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8454545454545455</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8909090909090909</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.9074074074074073</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.9225589225589226</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.7978723404255319</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.9493670886075949</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.8670520231213873</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.9741028916502148</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.9062100970713824</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.9311055626524213</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9802955665024631</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.9128440366972477</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9453681710213777</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>0.013063907623291016, 0.007848978042602539, 0.00787973403930664, 0.008481979370117188, 0.008769035339355469, 0.008087158203125, 0.0076961517333984375</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.00883242062159947</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.008087158203125</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.001762854953079524</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>0.007668018341064453, 0.007195234298706055, 0.006972074508666992, 0.007093906402587891, 0.00716400146484375, 0.007760763168334961, 0.007767915725708008</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.007374559129987445</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.007195234298706055</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.0003178618362163662</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7169811320754716, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8867924528301887, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>0.8487179487179488, 0.6703296703296704, 0.8901098901098901, 0.8159340659340659, 0.8315018315018314, 0.8543956043956045, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.8371009942438514</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.8487179487179488</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.0792774591420497</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.8601876809423981</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.06451450811633495</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>0.7741935483870969, 0.5161290322580646, 0.8275862068965518, 0.7096774193548386, 0.7692307692307692, 0.7857142857142857, 0.8750000000000001</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.8, 0.935064935064935, 0.8799999999999999, 0.9249999999999999, 0.9230769230769231, 0.945945945945946</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.9025969590255306</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.04618837091351537</v>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>0.841642228739003, 0.6580645161290324, 0.8813255709807435, 0.7948387096774192, 0.8471153846153845, 0.8543956043956045, 0.910472972972973</t>
+        </is>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.8268364267871656</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.8471153846153845</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.07640297917972334</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.7510758945488011</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.7741935483870969</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.1070305144688828</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>0.75, 0.47058823529411764, 0.8, 0.6470588235294118, 0.8333333333333334, 0.7857142857142857, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.8333333333333334, 0.9473684210526315, 0.9166666666666666, 0.9024390243902439, 0.9230769230769231, 1.0</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.9205624285855352</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.04627248760636481</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0.7234960650927037</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0.1166448637636054</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>0.8, 0.5714285714285714, 0.8571428571428571, 0.7857142857142857, 0.7142857142857143, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.7692307692307693, 0.9230769230769231, 0.8461538461538461, 0.9487179487179487, 0.9230769230769231, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.8864468864468866</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0.05627213002101544</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0.7877551020408163</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0.1208397660660201</v>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>0.9487179487179488, 0.8177655677655676, 0.9313186813186813, 0.9184981684981686, 0.9505494505494505, 0.8818681318681318, 0.9569597069597069</t>
+        </is>
+      </c>
+      <c r="BR21" t="n">
+        <v>0.9150968079539509</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0.9313186813186813</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0.04627866979580035</v>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>0.9025157232704403, 0.9184952978056427, 0.896551724137931, 0.8871473354231975, 0.9059561128526645, 0.9059561128526645, 0.9122257053291536</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>0.8994200244200244, 0.9182252388134741, 0.8920311714429361, 0.8856209150326797, 0.8946958270487682, 0.9171694318753143, 0.9139517345399698</t>
+        </is>
+      </c>
+      <c r="BW21" t="n">
+        <v>0.9030163347390239</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0.8994200244200244</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0.01228612821749656</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0.9041211445245277</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0.9059561128526645</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>0.009464354960405751</v>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>0.8287292817679559, 0.8571428571428571, 0.8196721311475409, 0.8064516129032258, 0.8314606741573034, 0.8421052631578947, 0.8478260869565216</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>0.9318681318681319, 0.9429824561403509, 0.9274725274725275, 0.9203539823008849, 0.9347826086956522, 0.9330357142857143, 0.9383259911894274</t>
+        </is>
+      </c>
+      <c r="CE21" t="n">
+        <v>0.9326887731360983</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0.9330357142857143</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0.006785198055288565</v>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>0.8802987068180439, 0.900062656641604, 0.8735723293100341, 0.8634027976020553, 0.8831216414264778, 0.8875704887218046, 0.8930760390729745</t>
+        </is>
+      </c>
+      <c r="CI21" t="n">
+        <v>0.8830149513704278</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>0.8831216414264778</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.01129975799599993</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>0.833341129604757</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>0.8314606741573034</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>0.01598141393996072</v>
+      </c>
+      <c r="CO21" t="inlineStr">
+        <is>
+          <t>0.7731958762886598, 0.8041237113402062, 0.7653061224489796, 0.7425742574257426, 0.7956989247311828, 0.7619047619047619, 0.7878787878787878</t>
+        </is>
+      </c>
+      <c r="CP21" t="inlineStr">
+        <is>
+          <t>0.9592760180995475, 0.9684684684684685, 0.9547511312217195, 0.9541284403669725, 0.9513274336283186, 0.9766355140186916, 0.9681818181818181</t>
+        </is>
+      </c>
+      <c r="CQ21" t="n">
+        <v>0.9618241177122194</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>0.9592760180995475</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>0.008700320099783172</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>0.7758117774311888</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>0.7731958762886598</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>0.01984952864823643</v>
+      </c>
+      <c r="CW21" t="inlineStr">
+        <is>
+          <t>0.8928571428571429, 0.9176470588235294, 0.8823529411764706, 0.8823529411764706, 0.8705882352941177, 0.9411764705882353, 0.9176470588235294</t>
+        </is>
+      </c>
+      <c r="CX21" t="inlineStr">
+        <is>
+          <t>0.905982905982906, 0.9188034188034188, 0.9017094017094017, 0.8888888888888888, 0.9188034188034188, 0.8931623931623932, 0.9102564102564102</t>
+        </is>
+      </c>
+      <c r="CY21" t="n">
+        <v>0.9053724053724055</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>0.905982905982906</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>0.01081809838014</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>0.9006602641056424</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>0.02346485865240459</v>
+      </c>
+      <c r="DE21" t="inlineStr">
+        <is>
+          <t>0.9747150997150996, 0.9801407742584213, 0.9698843640020111, 0.9688536953242836, 0.9748114630467571, 0.9748366013071895, 0.9795123177476118</t>
+        </is>
+      </c>
+      <c r="DF21" t="n">
+        <v>0.974679187914482</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>0.9748114630467571</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>0.003966976808432684</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SVC_splashing_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 8, 'sampling_strategy': 0.9199999999999999}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8659793814432989</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8935185185185186</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8103481812876872</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8078703703703703</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.7547169811320754</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8855218855218855</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.9488636363636364</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.8697916666666666</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.9076086956521739</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.9512152777777778</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.8785831088880339</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.8920386904761904</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.7933884297520661</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.8495575221238939</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>0.019039154052734375, 0.017574071884155273, 0.016163110733032227, 0.01656198501586914, 0.016521930694580078, 0.016611099243164062, 0.01680922508239746</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.0170400823865618</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.01661109924316406</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.000909072643262722</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>0.008915901184082031, 0.007719755172729492, 0.007328987121582031, 0.0072290897369384766, 0.007415056228637695, 0.007272958755493164, 0.0075299739837646484</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.007630246026175362</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.007415056228637695</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.0005472815537604288</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.9245283018867925, 0.8490566037735849, 0.8867924528301887, 0.8490566037735849, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>0.9067669172932331, 0.788888888888889, 0.9295665634674922, 0.8707430340557275, 0.8885448916408669, 0.8707430340557275, 0.8475232198142415</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.8718252213165967</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.8707430340557275</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.04192833487712379</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.8681241888789059</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.0442199725077206</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.8358208955223881, 0.9393939393939394, 0.8709677419354839, 0.9090909090909091, 0.8709677419354839, 0.8787878787878787</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.717948717948718, 0.9, 0.8181818181818181, 0.8500000000000001, 0.8181818181818181, 0.8</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.8276001776001776</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.05664729958766695</v>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.776884806735553, 0.9196969696969697, 0.8445747800586509, 0.8795454545454546, 0.8445747800586509, 0.8393939393939394</t>
+        </is>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.8601910567365552</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.8445747800586509</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.04623732024230981</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.8927819358729325</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.8787878787878787</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.03683900909433199</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.875, 0.96875, 0.9642857142857143, 0.9375, 0.9642857142857143, 0.90625</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>0.9411764705882353, 0.6666666666666666, 0.8571428571428571, 0.72, 0.8095238095238095, 0.72, 0.7619047619047619</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.78234493797519</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0.08712382104605663</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0.9335700496414782</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0.03280128260774139</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8, 0.9117647058823529, 0.7941176470588235, 0.8823529411764706, 0.7941176470588235, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.7777777777777778, 0.9473684210526315, 0.9473684210526315, 0.8947368421052632, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK22" t="n">
+        <v>0.885547201336675</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0.06203534909185286</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0.8581032412965185</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0.06313384566326838</v>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>0.9819548872180451, 0.8698412698412699, 0.9427244582043344, 0.9140866873065016, 0.956656346749226, 0.9349845201238389, 0.8715170278637772</t>
+        </is>
+      </c>
+      <c r="BR22" t="n">
+        <v>0.9245378853295704</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0.9349845201238389</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0.03906103263517107</v>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>0.8679245283018868, 0.8934169278996865, 0.8714733542319749, 0.877742946708464, 0.8683385579937304, 0.8746081504702194, 0.877742946708464</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>0.8757176775307576, 0.8956568249893025, 0.8765143053526935, 0.8773734856946473, 0.8740871208866741, 0.8789414898187129, 0.8853638628748174</t>
+        </is>
+      </c>
+      <c r="BW22" t="n">
+        <v>0.8805221095925152</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0.8773734856946473</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0.007025143803439958</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0.8758924874734895</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0.8746081504702194</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>0.008068305673627801</v>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>0.8923076923076924, 0.914572864321608, 0.8962025316455696, 0.9027431421446385, 0.8934010152284263, 0.898989898989899, 0.9007633587786259</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>0.8292682926829268, 0.8583333333333333, 0.831275720164609, 0.8354430379746836, 0.8278688524590163, 0.8347107438016528, 0.8408163265306122</t>
+        </is>
+      </c>
+      <c r="CE22" t="n">
+        <v>0.8368166152781191</v>
+      </c>
+      <c r="CF22" t="n">
+        <v>0.8347107438016528</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>0.009658670474772812</v>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>0.8607879924953096, 0.8864530988274706, 0.8637391259050893, 0.869093090059661, 0.8606349338437214, 0.8668503213957759, 0.870789842654619</t>
+        </is>
+      </c>
+      <c r="CI22" t="n">
+        <v>0.8683354864545211</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>0.8668503213957759</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>0.008232697239006808</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>0.8998543576309227</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>0.898989898989899</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>0.006953793473359946</v>
+      </c>
+      <c r="CO22" t="inlineStr">
+        <is>
+          <t>0.9405405405405406, 0.9430051813471503, 0.9365079365079365, 0.9282051282051282, 0.9361702127659575, 0.9368421052631579, 0.946524064171123</t>
+        </is>
+      </c>
+      <c r="CP22" t="inlineStr">
+        <is>
+          <t>0.7669172932330827, 0.8174603174603174, 0.7769230769230769, 0.7983870967741935, 0.7709923664122137, 0.7829457364341085, 0.7803030303030303</t>
+        </is>
+      </c>
+      <c r="CQ22" t="n">
+        <v>0.7848469882200033</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>0.7803030303030303</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>0.0162456102805097</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>0.9382564526858562</v>
+      </c>
+      <c r="CU22" t="n">
+        <v>0.9368421052631579</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>0.005432180424820598</v>
+      </c>
+      <c r="CW22" t="inlineStr">
+        <is>
+          <t>0.848780487804878, 0.8878048780487805, 0.8592233009708737, 0.8786407766990292, 0.8543689320388349, 0.8640776699029126, 0.8592233009708737</t>
+        </is>
+      </c>
+      <c r="CX22" t="inlineStr">
+        <is>
+          <t>0.9026548672566371, 0.9035087719298246, 0.8938053097345132, 0.8761061946902655, 0.8938053097345132, 0.8938053097345132, 0.911504424778761</t>
+        </is>
+      </c>
+      <c r="CY22" t="n">
+        <v>0.8964557411227183</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>0.8938053097345132</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>0.01034971143702066</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>0.8645884780623119</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>0.8592233009708737</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>0.01280976846915202</v>
+      </c>
+      <c r="DE22" t="inlineStr">
+        <is>
+          <t>0.9383336930714441, 0.9589644843816859, 0.9424993556147435, 0.9463656671535355, 0.9388693186699889, 0.9474181630724289, 0.9505756508291091</t>
+        </is>
+      </c>
+      <c r="DF22" t="n">
+        <v>0.9461466189704195</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>0.9463656671535355</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>0.006685616161022678</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 4, 'sampling_strategy': 0.72}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7826086956521738</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9527272727272728</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8432274247491638</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.8772727272727272</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.9591836734693877</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.9038461538461537</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8922558922558923</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.7473684210526316</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.8987341772151899</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.8160919540229885</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.9628382301707118</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.8699507389162562</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.894321217047962</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.9603960396039604</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.8899082568807339</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.9238095238095239</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>0.019942760467529297, 0.015845060348510742, 0.016435861587524414, 0.015941143035888672, 0.015973806381225586, 0.015646934509277344, 0.016431808471679688</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.01660248211451939</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.01597380638122559</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.001390463071889923</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>0.00785517692565918, 0.0070858001708984375, 0.007762908935546875, 0.007297039031982422, 0.0073490142822265625, 0.007215023040771484, 0.007570981979370117</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.007447992052350726</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.007349014282226562</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.0002667635708703914</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7547169811320755, 0.9056603773584906, 0.8679245283018868, 0.9433962264150944, 0.8490566037735849, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>0.9358974358974359, 0.7646520146520146, 0.8901098901098901, 0.8644688644688645, 0.9615384615384616, 0.8287545787545787, 0.9102564102564102</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.8793825222396651</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.8901098901098901</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.06206045719579769</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.8708695218129181</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.05579311998973876</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>0.8571428571428571, 0.6285714285714286, 0.8275862068965518, 0.7741935483870968, 0.9032258064516129, 0.7333333333333334, 0.8</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>0.9315068493150686, 0.8169014084507042, 0.935064935064935, 0.9066666666666667, 0.9600000000000001, 0.8947368421052632, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.9066121646152661</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.9066666666666667</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.04225042874661105</v>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>0.8943248532289628, 0.7227364185110664, 0.8813255709807435, 0.8404301075268817, 0.9316129032258065, 0.8140350877192983, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.8478813095064102</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.8507042253521127</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.06228597744295806</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.7891504543975544</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.08311442720203079</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>0.75, 0.5238095238095238, 0.8, 0.7058823529411765, 0.8235294117647058, 0.6875, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>1.0, 0.90625, 0.9473684210526315, 0.9444444444444444, 1.0, 0.918918918918919, 1.0</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>0.9595688263451422</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0.03737254233313052</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0.7081982793117246</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0.09229926495039717</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>1.0, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 1.0, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7435897435897436, 0.9230769230769231, 0.8717948717948718, 0.9230769230769231, 0.8717948717948718, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK23" t="n">
+        <v>0.8608058608058606</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0.05791717326315715</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0.09240188916466753</v>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>0.9641025641025641, 0.847985347985348, 0.9688644688644689, 0.924908424908425, 0.9615384615384616, 0.9304029304029304, 0.9926739926739926</t>
+        </is>
+      </c>
+      <c r="BR23" t="n">
+        <v>0.9414965986394559</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0.04379077349881157</v>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>0.8773584905660378, 0.8934169278996865, 0.8840125391849529, 0.8808777429467085, 0.896551724137931, 0.877742946708464, 0.890282131661442</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>0.8785103785103785, 0.9048768225238814, 0.9097033685268979, 0.8925842131724484, 0.8995223730517848, 0.886701860231272, 0.9139768728004023</t>
+        </is>
+      </c>
+      <c r="BW23" t="n">
+        <v>0.8979822698310093</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0.8995223730517848</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0.01182406421293969</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0.8857489290150318</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0.8840125391849529</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>0.007144300715650252</v>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>0.7914438502673796, 0.8229166666666666, 0.8159203980099502, 0.8041237113402062, 0.823529411764706, 0.7979274611398964, 0.8241206030150753</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>0.913140311804009, 0.9237668161434976, 0.9153318077803204, 0.9144144144144144, 0.926829268292683, 0.9123595505617978, 0.9202733485193623</t>
+        </is>
+      </c>
+      <c r="CE23" t="n">
+        <v>0.9180165025022978</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>0.9153318077803204</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>0.005234299886591206</v>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>0.8522920810356943, 0.8733417414050821, 0.8656261028951353, 0.8592690628773103, 0.8751793400286945, 0.8551435058508472, 0.8721969757672188</t>
+        </is>
+      </c>
+      <c r="CI23" t="n">
+        <v>0.8647212585514261</v>
+      </c>
+      <c r="CJ23" t="n">
+        <v>0.8656261028951353</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>0.008588476683258038</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>0.8114260146005543</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>0.8159203980099502</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>0.01250543216216009</v>
+      </c>
+      <c r="CO23" t="inlineStr">
+        <is>
+          <t>0.7184466019417476, 0.7383177570093458, 0.7068965517241379, 0.7155963302752294, 0.7549019607843137, 0.7129629629629629, 0.7192982456140351</t>
+        </is>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>0.9534883720930233, 0.9716981132075472, 0.9852216748768473, 0.9666666666666667, 0.9631336405529954, 0.9620853080568721, 0.9853658536585366</t>
+        </is>
+      </c>
+      <c r="CQ23" t="n">
+        <v>0.9696656613017841</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>0.01110626698555772</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>0.7237743443302532</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>0.7184466019417476</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>0.01557234463193047</v>
+      </c>
+      <c r="CW23" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9294117647058824, 0.9647058823529412, 0.9176470588235294, 0.9058823529411765, 0.9058823529411765, 0.9647058823529412</t>
+        </is>
+      </c>
+      <c r="CX23" t="inlineStr">
+        <is>
+          <t>0.8760683760683761, 0.8803418803418803, 0.8547008547008547, 0.8675213675213675, 0.8931623931623932, 0.8675213675213675, 0.8632478632478633</t>
+        </is>
+      </c>
+      <c r="CY23" t="n">
+        <v>0.871794871794872</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>0.8675213675213675</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>0.01164760929691021</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>0.9241696678671468</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>0.9176470588235294</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>0.02901472296304472</v>
+      </c>
+      <c r="DE23" t="inlineStr">
+        <is>
+          <t>0.9556369556369556, 0.9682252388134741, 0.9579688285570639, 0.9602815485168426, 0.9647561588738058, 0.9609854198089491, 0.9564605329311212</t>
+        </is>
+      </c>
+      <c r="DF23" t="n">
+        <v>0.9606163833054591</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>0.9602815485168426</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>0.004214872724060418</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 7, 'sampling_strategy': 0.75}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9583333333333333</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.9996775793650794</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>0.6237120628356934, 0.6292736530303955, 0.6760492324829102, 0.6121771335601807, 0.6123659610748291, 0.6093039512634277, 0.6382710933685303</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.6287361553737095</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.6237120628356934</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.02162923860708465</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>0.008033037185668945, 0.007374286651611328, 0.0075719356536865234, 0.007539033889770508, 0.007255077362060547, 0.007876157760620117, 0.007253885269165039</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.00755763053894043</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.007539033889770508</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.0002791405527033857</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8679245283018868, 0.9245283018867925, 0.8301886792452831, 0.9245283018867925, 0.9056603773584906, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8595238095238096, 0.9179566563467492, 0.8212074303405572, 0.9179566563467492, 0.903250773993808, 0.8506191950464397</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.8882689918072492</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.903250773993808</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.04178338171574328</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.8976739542777279</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.04156418206947522</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9411764705882353, 0.8656716417910447, 0.9411764705882353, 0.9253731343283583, 0.8985507246376812</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8108108108108109, 0.8947368421052632, 0.7692307692307692, 0.8947368421052632, 0.8717948717948718, 0.8108108108108109</t>
+        </is>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.8566521987574619</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.05692480140574064</v>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8546807677242461, 0.9179566563467492, 0.8174512055109069, 0.9179566563467492, 0.898584003061615, 0.8546807677242461</t>
+        </is>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.8885204842925493</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.898584003061615</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.0447998405178994</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.920388769827637</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.9253731343283583</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.03278408197902512</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9411764705882353, 0.8787878787878788, 0.9411764705882353, 0.9393939393939394, 0.8857142857142857</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>1.0, 0.7894736842105263, 0.8947368421052632, 0.75, 0.8947368421052632, 0.85, 0.8333333333333334</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.8588972431077693</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0.07548874676731257</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0.9205656709858392</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0.02641896540591721</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.9411764705882353, 0.9117647058823529, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8947368421052632, 0.7894736842105263, 0.8947368421052632, 0.8947368421052632, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK24" t="n">
+        <v>0.8558897243107769</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0.04685443382416019</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0.9206482593037215</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0.04326328084764177</v>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9396825396825397, 0.9845201238390093, 0.9458204334365325, 0.956656346749226, 0.9427244582043344, 0.9458204334365325</t>
+        </is>
+      </c>
+      <c r="BR24" t="n">
+        <v>0.9591029394213824</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0.9458204334365325</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0.02138793972833302</v>
+      </c>
+      <c r="BU24" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 0.9956140350877193, 0.995575221238938, 0.9931480367729186, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW24" t="n">
+        <v>0.9958661366880558</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0.001885242517235258</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0.9968637954974975</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>0.001675622622249898</v>
+      </c>
+      <c r="CC24" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 0.9975669099756691, 0.9975786924939467, 0.9951456310679612, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 0.9955947136563876, 0.9955555555555555, 0.9911504424778761, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE24" t="n">
+        <v>0.9955667683366408</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>0.002365186821933608</v>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 0.9965808118160284, 0.9965671240247511, 0.9931480367729186, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI24" t="n">
+        <v>0.9965702076326874</v>
+      </c>
+      <c r="CJ24" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>0.001831273974945286</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>0.9975736469287341</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>0.001297393947929273</v>
+      </c>
+      <c r="CO24" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 0.9951456310679612, 0.9951690821256038, 0.9951456310679612, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9911504424778761, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ24" t="n">
+        <v>0.9987357774968394</v>
+      </c>
+      <c r="CR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>0.003096700054087461</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>0.9958491627972421</v>
+      </c>
+      <c r="CU24" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>0.001694606963530478</v>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9951456310679612, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9912280701754386, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY24" t="n">
+        <v>0.9924257546521169</v>
+      </c>
+      <c r="CZ24" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA24" t="n">
+        <v>0.003092288713291248</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>0.9993065187239945</v>
+      </c>
+      <c r="DC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>0.001698675272387779</v>
+      </c>
+      <c r="DE24" t="inlineStr">
+        <is>
+          <t>0.9993740556874595, 0.9999572100984168, 0.9995918893375719, 0.9995918893375719, 0.9993770942520835, 1.0, 0.9995489303204742</t>
+        </is>
+      </c>
+      <c r="DF24" t="n">
+        <v>0.9996344384333682</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>0.9995918893375719</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>0.0002338419787687481</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 5, 'sampling_strategy': 0.61}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9872727272727273</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9160886104273886</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9227272727272727</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.9541284403669724</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9937106918238994</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.9999419347346418</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.9957059206245933</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.9977064220183487</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.9977011494252873</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>0.603410005569458, 0.6189558506011963, 0.6579363346099854, 0.6508758068084717, 0.6773171424865723, 0.6623191833496094, 0.6698668003082275</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.6486687319619315</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.6579363346099854</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.02529367967902623</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>0.006873130798339844, 0.006659984588623047, 0.007131814956665039, 0.006452083587646484, 0.006824970245361328, 0.0076940059661865234, 0.006478071212768555</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.006873437336512974</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.006824970245361328</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.0004003313721264312</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8301886792452831, 0.9245283018867925, 0.8867924528301887, 0.9433962264150944, 0.9245283018867925, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>0.9205128205128206, 0.8388278388278387, 0.88003663003663, 0.8772893772893773, 0.8928571428571428, 0.9029304029304028, 0.9386446886446886</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.8930141287284146</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.8928571428571428</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.02997265534745976</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.9138963761605271</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.03898963905964822</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>0.896551724137931, 0.7272727272727273, 0.8461538461538461, 0.7999999999999999, 0.88, 0.8571428571428571, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>0.9620253164556962, 0.8767123287671232, 0.9500000000000001, 0.9210526315789475, 0.962962962962963, 0.9487179487179487, 0.9610389610389611</t>
+        </is>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.9403585927888057</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.02926354319701806</v>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>0.9292885202968136, 0.8019925280199253, 0.8980769230769231, 0.8605263157894737, 0.9214814814814816, 0.9029304029304028, 0.9287953425884461</t>
+        </is>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.8918702163119236</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.9029304029304028</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.04286475631591891</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.8433818398350417</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.05676432797263074</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>0.9285714285714286, 0.631578947368421, 0.9166666666666666, 0.75, 1.0, 0.8571428571428571, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>0.95, 0.9411764705882353, 0.926829268292683, 0.9459459459459459, 0.9285714285714286, 0.9487179487179487, 0.9736842105263158</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.9449893246632225</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0.9459459459459459</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0.01452679258329168</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0.8500895094880055</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0.1141142361014914</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.8205128205128205, 0.9743589743589743, 0.8974358974358975, 1.0, 0.9487179487179487, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK25" t="n">
+        <v>0.9377289377289377</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0.05627213002101544</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0.8482993197278912</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0.04605798878860071</v>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.8974358974358974, 0.9871794871794871, 0.924908424908425, 0.9945054945054945, 0.9194139194139194, 0.9926739926739926</t>
+        </is>
+      </c>
+      <c r="BR25" t="n">
+        <v>0.9557823129251701</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0.9743589743589743</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0.03755285215700504</v>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>0.9905660377358491, 0.9968652037617555, 0.9968652037617555, 1.0, 0.987460815047022, 0.9968652037617555, 0.9905956112852664</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>0.9897741147741148, 0.9978632478632479, 0.9978632478632479, 1.0, 0.9877073906485672, 0.9978632478632479, 0.9898441427853193</t>
+        </is>
+      </c>
+      <c r="BW25" t="n">
+        <v>0.9944164845425351</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0.9978632478632479</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0.004694769492597695</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0.9941740107647721</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>0.004252043521602449</v>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>0.9822485207100591, 0.9941520467836257, 0.9941520467836257, 1.0, 0.9767441860465116, 0.9941520467836257, 0.9824561403508771</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>0.9935760171306209, 0.9978586723768736, 0.9978586723768736, 1.0, 0.9914163090128757, 0.9978586723768736, 0.9935760171306209</t>
+        </is>
+      </c>
+      <c r="CE25" t="n">
+        <v>0.9960206229149627</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>0.9978586723768736</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>0.002906215527570407</v>
+      </c>
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>0.98791226892034, 0.9960053595802496, 0.9960053595802496, 1.0, 0.9840802475296937, 0.9960053595802496, 0.988016078740749</t>
+        </is>
+      </c>
+      <c r="CI25" t="n">
+        <v>0.9925749534187903</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>0.9960053595802496</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>0.005413189833773676</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>0.9891292839226179</v>
+      </c>
+      <c r="CM25" t="n">
+        <v>0.9941520467836257</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>0.00792034726174041</v>
+      </c>
+      <c r="CO25" t="inlineStr">
+        <is>
+          <t>0.9764705882352941, 0.9883720930232558, 0.9883720930232558, 1.0, 0.9655172413793104, 0.9883720930232558, 0.9767441860465116</t>
+        </is>
+      </c>
+      <c r="CP25" t="inlineStr">
+        <is>
+          <t>0.9957081545064378, 1.0, 1.0, 1.0, 0.9956896551724138, 1.0, 0.9957081545064378</t>
+        </is>
+      </c>
+      <c r="CQ25" t="n">
+        <v>0.9981579948836128</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>0.002126971961409068</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>0.9834068992472691</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>0.9883720930232558</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>0.01043232926033697</v>
+      </c>
+      <c r="CW25" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 1.0, 0.9882352941176471, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CX25" t="inlineStr">
+        <is>
+          <t>0.9914529914529915, 0.9957264957264957, 0.9957264957264957, 1.0, 0.9871794871794872, 0.9957264957264957, 0.9914529914529915</t>
+        </is>
+      </c>
+      <c r="CY25" t="n">
+        <v>0.9938949938949939</v>
+      </c>
+      <c r="CZ25" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="DA25" t="n">
+        <v>0.003861144884210462</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>0.9949379751900761</v>
+      </c>
+      <c r="DC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>0.005845282576227087</v>
+      </c>
+      <c r="DE25" t="inlineStr">
+        <is>
+          <t>0.9998473748473748, 0.9999497234791351, 0.9999497234791352, 1.0, 0.9996983408748115, 1.0, 0.999798893916541</t>
+        </is>
+      </c>
+      <c r="DF25" t="n">
+        <v>0.9998920080852854</v>
+      </c>
+      <c r="DG25" t="n">
+        <v>0.9999497234791351</v>
+      </c>
+      <c r="DH25" t="n">
+        <v>0.0001056652419010312</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'estimator': 'XGBClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 7, 'sampling_strategy': 0.83}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.939429012345679</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8680555555555556</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>0.2366790771484375, 0.3407421112060547, 0.2813689708709717, 0.2294921875, 0.2319340705871582, 0.22330307960510254, 0.2231590747833252</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.25238265310015</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.2319340705871582</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.04059549556086792</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>0.007437944412231445, 0.007461071014404297, 0.007288932800292969, 0.0075070858001708984, 0.007315874099731445, 0.007239818572998047, 0.007155895233154297</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.007343803133283343</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.007315874099731445</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.0001190369196730556</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8301886792452831, 0.9056603773584906, 0.8301886792452831, 0.9245283018867925, 0.7924528301886793, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8444444444444444, 0.903250773993808, 0.8212074303405572, 0.9179566563467492, 0.8150154798761611, 0.8243034055727554</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.8676495159467296</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.8444444444444444</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.04999704488060646</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.8707197763801539</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.05670167050740303</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8615384615384616, 0.9253731343283583, 0.8656716417910447, 0.9411764705882353, 0.819672131147541, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7804878048780488, 0.8717948717948718, 0.7692307692307692, 0.8947368421052632, 0.7555555555555555, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.8277182951123901</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.06908819449959533</v>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8210131332082552, 0.898584003061615, 0.8174512055109069, 0.9179566563467492, 0.7876138433515483, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU26" t="n">
+        <v>0.8618140295083485</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.8317460317460318</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.05838606355402311</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.8959097639043071</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.8857142857142858</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.04892065164911274</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9333333333333333, 0.9393939393939394, 0.8787878787878788, 0.9411764705882353, 0.9259259259259259, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>1.0, 0.6956521739130435, 0.85, 0.75, 0.8947368421052632, 0.6538461538461539, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>0.8096806545184523</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0.1109196057134349</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0.9179535150123385</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0.03127682332795068</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.9117647058823529, 0.8529411764705882, 0.9411764705882353, 0.7352941176470589, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8888888888888888, 0.8947368421052632, 0.7894736842105263, 0.8947368421052632, 0.8947368421052632, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK26" t="n">
+        <v>0.8563074352548036</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0.0606012066276429</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0.8789915966386556</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0.08300207209993776</v>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>0.9834586466165414, 0.9523809523809524, 0.9744582043343653, 0.9427244582043344, 0.9504643962848297, 0.9195046439628484, 0.9303405572755419</t>
+        </is>
+      </c>
+      <c r="BR26" t="n">
+        <v>0.9504759798656305</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0.9504643962848297</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0.02101488394136693</v>
+      </c>
+      <c r="BU26" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV26" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW26" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC26" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD26" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE26" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI26" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM26" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO26" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP26" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU26" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW26" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX26" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY26" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE26" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="DF26" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>9.712984233453662e-06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'estimator': 'XGBClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 3, 'sampling_strategy': 0.99}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9772727272727273</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8825240545983442</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.8886363636363637</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.9357798165137615</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>0.2303171157836914, 0.2195756435394287, 0.22932195663452148, 0.21951723098754883, 0.23137784004211426, 0.23183512687683105, 0.23522686958312988</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.2281673976353236</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.2303171157836914</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.005709556381276731</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>0.006620883941650391, 0.0068302154541015625, 0.006826162338256836, 0.00671696662902832, 0.006688117980957031, 0.007075786590576172, 0.0067479610443115234</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.006786584854125977</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.006747961044311523</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.0001365904537175735</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8490566037735849, 0.9056603773584906, 0.8679245283018868, 0.9433962264150944, 0.9056603773584906, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>0.8410256410256409, 0.8287545787545787, 0.8901098901098901, 0.8644688644688645, 0.9157509157509157, 0.8672161172161172, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.8761643118785976</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.03365145530174389</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.897873614854747</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.02991612441849606</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>0.7857142857142856, 0.7333333333333334, 0.8275862068965518, 0.7741935483870968, 0.888888888888889, 0.8148148148148148, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>0.9249999999999999, 0.8947368421052632, 0.935064935064935, 0.9066666666666667, 0.9620253164556962, 0.9367088607594937, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.9296530060149552</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.935064935064935</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.02141440516243095</v>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>0.8553571428571427, 0.8140350877192983, 0.8813255709807435, 0.8404301075268817, 0.9254571026722926, 0.8757618377871542, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU27" t="n">
+        <v>0.8713406276290231</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.03548749952673118</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.8130282492430911</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.04993210910089845</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.6875, 0.8, 0.7058823529411765, 0.9230769230769231, 0.8461538461538461, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>0.9024390243902439, 0.918918918918919, 0.9473684210526315, 0.9444444444444444, 0.95, 0.925, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>0.9373062545398874</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0.02168181818279246</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0.803038138332256</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0.07654532132746722</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8717948717948718, 0.9230769230769231, 0.8717948717948718, 0.9743589743589743, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK27" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0.03626188621469473</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0.8292517006802721</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0.05998750390489416</v>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>0.9743589743589745, 0.9194139194139195, 0.9688644688644689, 0.9432234432234432, 0.9908424908424909, 0.9395604395604397, 0.9816849816849816</t>
+        </is>
+      </c>
+      <c r="BR27" t="n">
+        <v>0.9597069597069597</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0.9688644688644689</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0.02405978845122478</v>
+      </c>
+      <c r="BU27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_splashing_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'estimator': 'AdaBoostClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 10, 'sampling_strategy': 0.9199999999999999}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8530092592592593</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7811709784088698</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.7789351851851851</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.7169811320754716</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.9595959595959596</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.9639175257731959</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.9739583333333334</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.9689119170984456</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.9943948412698413</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.955609804703069</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.9536458333333333</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.9514563106796117</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>0.0371098518371582, 0.03479790687561035, 0.03462982177734375, 0.03500676155090332, 0.035021066665649414, 0.0361478328704834, 0.03560495376586914</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.03547402790614537</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.03502106666564941</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.0008229224934824869</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>0.015568017959594727, 0.009377002716064453, 0.009443998336791992, 0.009479045867919922, 0.009800910949707031, 0.009428977966308594, 0.009467840194702148</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.01036654199872698</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.009467840194702148</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.002127369471733603</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7924528301886793, 0.8679245283018868, 0.7924528301886793, 0.9056603773584906, 0.7735849056603774, 0.7735849056603774</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.788888888888889, 0.8506191950464397, 0.791795665634675, 0.903250773993808, 0.8003095975232198, 0.7538699690402477</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.8186913361835962</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.8003095975232198</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.04608867165466955</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.8277927523210542</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.0531594177218481</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>0.9210526315789475, 0.8358208955223881, 0.8985507246376812, 0.8307692307692308, 0.9253731343283583, 0.8000000000000002, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>0.8125000000000001, 0.717948717948718, 0.8108108108108109, 0.7317073170731707, 0.8717948717948718, 0.7391304347826088, 0.6842105263157895</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.7668718112465671</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.7391304347826088</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.06124179085427565</v>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>0.8667763157894738, 0.776884806735553, 0.8546807677242461, 0.7812382739212007, 0.898584003061615, 0.7695652173913045, 0.7538699690402477</t>
+        </is>
+      </c>
+      <c r="AU28" t="n">
+        <v>0.8145141933805201</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.7812382739212007</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.05296064033987335</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.8621565755144731</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.8358208955223881</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.04754523249114818</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>0.8536585365853658, 0.875, 0.8857142857142857, 0.8709677419354839, 0.9393939393939394, 0.9230769230769231, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>1.0, 0.6666666666666666, 0.8333333333333334, 0.6818181818181818, 0.85, 0.6296296296296297, 0.6842105263157895</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>0.7636654768233715</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0.1245263674502841</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0.8816201197815292</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0.03661951587257762</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.9117647058823529, 0.7941176470588235, 0.9117647058823529, 0.7058823529411765, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>0.6842105263157895, 0.7777777777777778, 0.7894736842105263, 0.7894736842105263, 0.8947368421052632, 0.8947368421052632, 0.6842105263157895</t>
+        </is>
+      </c>
+      <c r="BK28" t="n">
+        <v>0.7878028404344194</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0.07967665174647527</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0.8495798319327731</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0.09041329516848916</v>
+      </c>
+      <c r="BQ28" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8904761904761905, 0.9481424148606812, 0.8900928792569659, 0.9458204334365325, 0.8072755417956657, 0.871517027863777</t>
+        </is>
+      </c>
+      <c r="BR28" t="n">
+        <v>0.8994545186495652</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0.8904761904761905</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0.04758423345386659</v>
+      </c>
+      <c r="BU28" t="inlineStr">
+        <is>
+          <t>0.9056603773584906, 0.9090909090909091, 0.9059561128526645, 0.9247648902821317, 0.9278996865203761, 0.9467084639498433, 0.9059561128526645</t>
+        </is>
+      </c>
+      <c r="BV28" t="inlineStr">
+        <is>
+          <t>0.9049859702136844, 0.9136927685066325, 0.9032133344789071, 0.9197740355700661, 0.9321891915112983, 0.9487498926024573, 0.895222957298737</t>
+        </is>
+      </c>
+      <c r="BW28" t="n">
+        <v>0.9168325928831118</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0.9136927685066325</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0.01717911000205646</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0.9180052218438686</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CB28" t="n">
+        <v>0.01458811584922898</v>
+      </c>
+      <c r="CC28" t="inlineStr">
+        <is>
+          <t>0.9253731343283582, 0.9269521410579346, 0.9261083743842364, 0.9414634146341464, 0.9426433915211971, 0.9580246913580247, 0.927536231884058</t>
+        </is>
+      </c>
+      <c r="CD28" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.8796680497925311, 0.8706896551724138, 0.8947368421052632, 0.9029535864978903, 0.9270386266094421, 0.8660714285714286</t>
+        </is>
+      </c>
+      <c r="CE28" t="n">
+        <v>0.8875647229348343</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>0.8796680497925311</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>0.02036881633681616</v>
+      </c>
+      <c r="CH28" t="inlineStr">
+        <is>
+          <t>0.898584003061615, 0.9033100954252329, 0.8983990147783252, 0.9181001283697048, 0.9227984890095438, 0.9425316589837334, 0.8968038302277432</t>
+        </is>
+      </c>
+      <c r="CI28" t="n">
+        <v>0.9115038885508425</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>0.9033100954252329</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>0.01583708142052328</v>
+      </c>
+      <c r="CL28" t="n">
+        <v>0.9354430541668508</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>0.927536231884058</v>
+      </c>
+      <c r="CN28" t="n">
+        <v>0.01147153565905523</v>
+      </c>
+      <c r="CO28" t="inlineStr">
+        <is>
+          <t>0.9441624365482234, 0.9583333333333334, 0.94, 0.946078431372549, 0.9692307692307692, 0.9748743718592965, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="CP28" t="inlineStr">
+        <is>
+          <t>0.8429752066115702, 0.8346456692913385, 0.8487394957983193, 0.8869565217391304, 0.8629032258064516, 0.9, 0.8738738738738738</t>
+        </is>
+      </c>
+      <c r="CQ28" t="n">
+        <v>0.8642991418743835</v>
+      </c>
+      <c r="CR28" t="n">
+        <v>0.8629032258064516</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>0.02222506128903664</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>0.950822323631585</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>0.946078431372549</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>0.01659421461370501</v>
+      </c>
+      <c r="CW28" t="inlineStr">
+        <is>
+          <t>0.9073170731707317, 0.8975609756097561, 0.912621359223301, 0.9368932038834952, 0.9174757281553398, 0.941747572815534, 0.9320388349514563</t>
+        </is>
+      </c>
+      <c r="CX28" t="inlineStr">
+        <is>
+          <t>0.9026548672566371, 0.9298245614035088, 0.8938053097345132, 0.9026548672566371, 0.9469026548672567, 0.9557522123893806, 0.8584070796460177</t>
+        </is>
+      </c>
+      <c r="CY28" t="n">
+        <v>0.9128573646505644</v>
+      </c>
+      <c r="CZ28" t="n">
+        <v>0.9026548672566371</v>
+      </c>
+      <c r="DA28" t="n">
+        <v>0.03122025842730721</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>0.9208078211156592</v>
+      </c>
+      <c r="DC28" t="n">
+        <v>0.9174757281553398</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>0.01523100934522446</v>
+      </c>
+      <c r="DE28" t="inlineStr">
+        <is>
+          <t>0.9822793006691128, 0.983846812152332, 0.979014520147779, 0.9848999054901624, 0.978327175874216, 0.992138499871123, 0.9826015980754361</t>
+        </is>
+      </c>
+      <c r="DF28" t="n">
+        <v>0.983301116040023</v>
+      </c>
+      <c r="DG28" t="n">
+        <v>0.9826015980754361</v>
+      </c>
+      <c r="DH28" t="n">
+        <v>0.004235929347894764</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_no_fragmentation_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'estimator': 'AdaBoostClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 4, 'sampling_strategy': 0.77}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7555555555555556</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9422727272727274</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8253968253968254</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8522727272727273</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.8952380952380952</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.9595959595959596</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.9620253164556962</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.9946579955870398</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.9494611457742484</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.9603704563929858</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.9858490566037735</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.9587155963302753</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.9720930232558139</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>0.03625798225402832, 0.03450798988342285, 0.03415703773498535, 0.03495907783508301, 0.034290313720703125, 0.034620046615600586, 0.03487277030944824</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.03480931690761021</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.03462004661560059</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.0006487944426305423</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>0.008936882019042969, 0.008708953857421875, 0.00868988037109375, 0.008696794509887695, 0.008623838424682617, 0.01281118392944336, 0.008706092834472656</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.009310517992292131</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.008706092834472656</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.001432024113029118</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.7735849056603774, 0.8867924528301887, 0.8490566037735849, 0.8490566037735849, 0.9056603773584906, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>0.8025641025641026, 0.7545787545787546, 0.8543956043956045, 0.8745421245421245, 0.8287545787545787, 0.8672161172161172, 0.8516483516483516</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.8333856619570905</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.8516483516483516</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.039270566471881</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.8495058400718778</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.03885829061151106</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>0.7096774193548386, 0.6250000000000001, 0.7857142857142857, 0.7647058823529412, 0.7333333333333334, 0.8148148148148148, 0.75</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>0.8831168831168831, 0.8378378378378378, 0.9230769230769231, 0.8888888888888888, 0.8947368421052632, 0.9367088607594937, 0.8918918918918919</t>
+        </is>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.8937511610967402</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.8918918918918919</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.02921061940481568</v>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>0.7963971512358609, 0.731418918918919, 0.8543956043956045, 0.826797385620915, 0.8140350877192983, 0.8757618377871542, 0.8209459459459459</t>
+        </is>
+      </c>
+      <c r="AU29" t="n">
+        <v>0.8171074188033852</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.8209459459459459</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.04262838224887127</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.7404636765100305</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.05680144795320526</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>0.6875, 0.5555555555555556, 0.7857142857142857, 0.65, 0.6875, 0.8461538461538461, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8857142857142857, 0.9230769230769231, 0.9696969696969697, 0.918918918918919, 0.925, 0.9428571428571428</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>0.9228572974813577</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0.02614372986067533</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0.6970129077271935</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0.08736886918717822</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7142857142857143, 0.7857142857142857, 0.9285714285714286, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7948717948717948, 0.9230769230769231, 0.8205128205128205, 0.8717948717948718, 0.9487179487179487, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="BK29" t="n">
+        <v>0.8681318681318679</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0.05022457582711388</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0.7986394557823129</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0.06780917439116797</v>
+      </c>
+      <c r="BQ29" t="inlineStr">
+        <is>
+          <t>0.8940170940170942, 0.8882783882783882, 0.9597069597069597, 0.9267399267399268, 0.9212454212454212, 0.9230769230769231, 0.9505494505494505</t>
+        </is>
+      </c>
+      <c r="BR29" t="n">
+        <v>0.9233734519448806</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0.02440160277980927</v>
+      </c>
+      <c r="BU29" t="inlineStr">
+        <is>
+          <t>0.9528301886792453, 0.9561128526645768, 0.9623824451410659, 0.9655172413793104, 0.9592476489028213, 0.9498432601880877, 0.9561128526645768</t>
+        </is>
+      </c>
+      <c r="BV29" t="inlineStr">
+        <is>
+          <t>0.9526862026862026, 0.9625942684766213, 0.9631221719457014, 0.9652589240824535, 0.9647310206133735, 0.9508295625942684, 0.9625942684766213</t>
+        </is>
+      </c>
+      <c r="BW29" t="n">
+        <v>0.9602594884107489</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0.9625942684766213</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0.005481976543675265</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0.9574352128028121</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0.9561128526645768</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>0.005006003291618332</v>
+      </c>
+      <c r="CC29" t="inlineStr">
+        <is>
+          <t>0.9142857142857143, 0.9222222222222223, 0.9318181818181819, 0.9371428571428572, 0.9273743016759776, 0.9101123595505618, 0.9222222222222223</t>
+        </is>
+      </c>
+      <c r="CD29" t="inlineStr">
+        <is>
+          <t>0.9674620390455531, 0.9694323144104804, 0.974025974025974, 0.9762419006479482, 0.971677559912854, 0.9652173913043478, 0.9694323144104804</t>
+        </is>
+      </c>
+      <c r="CE29" t="n">
+        <v>0.9704984991082339</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0.9694323144104804</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0.003509245215766083</v>
+      </c>
+      <c r="CH29" t="inlineStr">
+        <is>
+          <t>0.9408738766656337, 0.9458272683163513, 0.952922077922078, 0.9566923788954027, 0.9495259307944157, 0.9376648754274548, 0.9458272683163513</t>
+        </is>
+      </c>
+      <c r="CI29" t="n">
+        <v>0.947047668048241</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>0.9458272683163513</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0.006127247964649358</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0.9235968369882482</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>0.9222222222222223</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>0.008764063649503672</v>
+      </c>
+      <c r="CO29" t="inlineStr">
+        <is>
+          <t>0.8791208791208791, 0.8736842105263158, 0.9010989010989011, 0.9111111111111111, 0.8829787234042553, 0.8709677419354839, 0.8736842105263158</t>
+        </is>
+      </c>
+      <c r="CP29" t="inlineStr">
+        <is>
+          <t>0.9823788546255506, 0.9910714285714286, 0.9868421052631579, 0.9868995633187773, 0.9911111111111112, 0.9823008849557522, 0.9910714285714286</t>
+        </is>
+      </c>
+      <c r="CQ29" t="n">
+        <v>0.9873821966310297</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>0.9868995633187773</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>0.003635213905766137</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>0.8846636825318946</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>0.8791208791208791</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>0.01430195313622783</v>
+      </c>
+      <c r="CW29" t="inlineStr">
+        <is>
+          <t>0.9523809523809523, 0.9764705882352941, 0.9647058823529412, 0.9647058823529412, 0.9764705882352941, 0.9529411764705882, 0.9764705882352941</t>
+        </is>
+      </c>
+      <c r="CX29" t="inlineStr">
+        <is>
+          <t>0.9529914529914529, 0.9487179487179487, 0.9615384615384616, 0.9658119658119658, 0.9529914529914529, 0.9487179487179487, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="CY29" t="n">
+        <v>0.9542124542124543</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>0.9529914529914529</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>0.006344508452633275</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>0.9663065226090436</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>0.9647058823529412</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>0.009911052792581183</v>
+      </c>
+      <c r="DE29" t="inlineStr">
+        <is>
+          <t>0.9941239316239316, 0.9950729009552539, 0.994017094017094, 0.995475113122172, 0.9962041226747109, 0.9930115635997989, 0.9952237305178482</t>
+        </is>
+      </c>
+      <c r="DF29" t="n">
+        <v>0.9947326366444014</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>0.9950729009552539</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>0.0009941335731977023</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_splashing_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'estimator': 'RandomForestClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 9, 'sampling_strategy': 0.98}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9340277777777778</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8068924539512775</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.7997685185185186</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.7450980392156864</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.9999751984126983</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>0.08723783493041992, 0.06588292121887207, 0.06459999084472656, 0.06614804267883301, 0.06572890281677246, 0.06564807891845703, 0.0644679069519043</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.06853052547999791</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.06572890281677246</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.007660296703003662</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>0.011517047882080078, 0.010032892227172852, 0.009844064712524414, 0.010617971420288086, 0.010041236877441406, 0.009868144989013672, 0.009877204895019531</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.01025693757193429</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.01003289222717285</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.0005708098402389202</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8867924528301887, 0.9245283018867925, 0.8490566037735849, 0.9245283018867925, 0.8490566037735849, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8873015873015873, 0.9179566563467492, 0.8475232198142415, 0.9179566563467492, 0.8707430340557275, 0.8390092879256965</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.8896941232633404</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.8873015873015873</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.03710231378897678</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.8949785364879704</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.04032871831483025</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.9117647058823529, 0.9411764705882353, 0.8787878787878787, 0.9411764705882353, 0.8709677419354839, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8421052631578948, 0.8947368421052632, 0.8, 0.8947368421052632, 0.8181818181818181, 0.7999999999999999</t>
+        </is>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.8563150299992406</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.0517108575312271</v>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8769349845201239, 0.9179566563467492, 0.8393939393939394, 0.9179566563467492, 0.8445747800586509, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.8865506536216655</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.8769349845201239</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.04223841225880259</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.9167862772440906</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.03394915788865599</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9393939393939394, 0.9411764705882353, 0.90625, 0.9411764705882353, 0.9642857142857143, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.8947368421052632, 0.7619047619047619, 0.8947368421052632, 0.72, 0.875</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.8494826351593269</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.08806383025438395</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0.9290133436667051</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0.03063072774934426</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.9411764705882353, 0.7941176470588235, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8888888888888888, 0.8947368421052632, 0.8421052631578947, 0.8947368421052632, 0.9473684210526315, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK30" t="n">
+        <v>0.8713450292397661</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0.06173083776745587</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0.9080432172869147</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0.06354226821463579</v>
+      </c>
+      <c r="BQ30" t="inlineStr">
+        <is>
+          <t>0.9939849624060151, 0.9523809523809523, 0.9837461300309597, 0.93343653250774, 0.9357585139318886, 0.923374613003096, 0.9404024767801858</t>
+        </is>
+      </c>
+      <c r="BR30" t="n">
+        <v>0.9518691687201197</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0.9404024767801858</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0.02487937375107739</v>
+      </c>
+      <c r="BU30" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV30" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW30" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC30" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD30" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE30" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH30" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI30" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO30" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP30" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW30" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX30" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY30" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE30" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914511, 0.9999785204914512, 0.9999785204914511, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF30" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>9.712984233463659e-06</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_no_fragmentation_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'estimator': 'RandomForestClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 5, 'sampling_strategy': 0.96}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9836363636363636</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9160886104273886</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.9227272727272727</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.9541284403669724</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>0.06667327880859375, 0.06545591354370117, 0.06612229347229004, 0.0656287670135498, 0.06633424758911133, 0.06550884246826172, 0.06645321846008301</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.06602522305079869</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.06612229347229004</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.0004560724845196614</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>0.009180784225463867, 0.009092092514038086, 0.008980989456176758, 0.008982181549072266, 0.009090662002563477, 0.009211301803588867, 0.009134769439697266</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.009096111570085798</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.009092092514038086</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>8.299025824317922e-05</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7924528301886793, 0.9056603773584906, 0.7924528301886793, 0.9245283018867925, 0.9245283018867925, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>0.8076923076923077, 0.7445054945054945, 0.8672161172161172, 0.7673992673992673, 0.9029304029304028, 0.9029304029304028, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.8454997383568813</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.06681434993459637</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.8763601876809425</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.05597929462586611</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>0.7407407407407408, 0.6206896551724138, 0.8148148148148148, 0.6451612903225806, 0.8571428571428571, 0.8571428571428571, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>0.9135802469135802, 0.8571428571428572, 0.9367088607594937, 0.8533333333333333, 0.9487179487179487, 0.9487179487179487, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.9150813738053991</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.9367088607594937</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.0395419949506318</v>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>0.8271604938271605, 0.7389162561576355, 0.8757618377871542, 0.749247311827957, 0.9029304029304028, 0.9029304029304028, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.8434234641886231</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.06785227367693537</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.7717655545718473</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.09654986398718275</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.6, 0.8461538461538461, 0.5882352941176471, 0.8571428571428571, 0.8571428571428571, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.868421052631579, 0.925, 0.8888888888888888, 0.9487179487179487, 0.9487179487179487, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.9190958846973885</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0.03708650245585334</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0.7706440268415058</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0.1125928375085998</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.6428571428571429, 0.7857142857142857, 0.7142857142857143, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8461538461538461, 0.9487179487179487, 0.8205128205128205, 0.9487179487179487, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK31" t="n">
+        <v>0.9120879120879122</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0.0510197372790627</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0.7789115646258503</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0.09997917317482359</v>
+      </c>
+      <c r="BQ31" t="inlineStr">
+        <is>
+          <t>0.9487179487179488, 0.8543956043956044, 0.9697802197802199, 0.9084249084249084, 0.989010989010989, 0.9184981684981686, 0.9844322344322345</t>
+        </is>
+      </c>
+      <c r="BR31" t="n">
+        <v>0.9390371533228675</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0.9487179487179488</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0.04491277708295126</v>
+      </c>
+      <c r="BU31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE31" t="inlineStr">
+        <is>
+          <t>0.9999999999999999, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH31" t="n">
+        <v>4.196248604251576e-17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_splashing_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LGBMClassifier', 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 5, 'sampling_strategy': 0.83}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9486882716049383</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.8366013071895425</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8287037037037037</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.7843137254901961</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>0.41130971908569336, 0.42592406272888184, 0.42369699478149414, 0.44514012336730957, 0.26281094551086426, 0.4556441307067871, 0.44167399406433105</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.4094571386064802</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.4259240627288818</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.06144324967470168</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>0.00863504409790039, 0.008233070373535156, 0.008351802825927734, 0.008562088012695312, 0.008033990859985352, 0.008355855941772461, 0.008805274963378906</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.008425303867885045</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.008355855941772461</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.0002412419958348862</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8867924528301887, 0.9622641509433962, 0.8301886792452831, 0.9056603773584906, 0.8867924528301887, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8738095238095238, 0.9589783281733746, 0.8212074303405572, 0.903250773993808, 0.8885448916408669, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.8957277647901265</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.8885448916408669</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.04336298389527568</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.9030647898572427</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.04343202722774474</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.9142857142857143, 0.9705882352941176, 0.8656716417910447, 0.9253731343283583, 0.9090909090909091, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8333333333333334, 0.9473684210526315, 0.7692307692307692, 0.8717948717948718, 0.8500000000000001, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.8654681575734208</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.05863239589276455</v>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8738095238095238, 0.9589783281733746, 0.8174512055109069, 0.898584003061615, 0.8795454545454546, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU32" t="n">
+        <v>0.8948052618506187</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0.8795454545454546</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.04651414035641593</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.9241423661278171</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.03457112365859396</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9142857142857143, 0.9705882352941176, 0.8787878787878788, 0.9393939393939394, 0.9375, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>1.0, 0.8333333333333334, 0.9473684210526315, 0.75, 0.85, 0.8095238095238095, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>0.8617615467239527</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0.07836790359028478</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0.9283237742271356</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0.02733039148211509</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>1.0, 0.9142857142857143, 0.9705882352941176, 0.8529411764705882, 0.9117647058823529, 0.8823529411764706, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.9473684210526315, 0.7894736842105263, 0.8947368421052632, 0.8947368421052632, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK32" t="n">
+        <v>0.8709273182957392</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0.04843646137866587</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0.9205282112845138</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0.04635221762438629</v>
+      </c>
+      <c r="BQ32" t="inlineStr">
+        <is>
+          <t>0.9804511278195489, 0.9444444444444444, 0.9845201238390093, 0.9520123839009288, 0.9597523219814241, 0.9164086687306502, 0.934984520123839</t>
+        </is>
+      </c>
+      <c r="BR32" t="n">
+        <v>0.9532247986914063</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0.9520123839009288</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0.02245623900588467</v>
+      </c>
+      <c r="BU32" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV32" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW32" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC32" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD32" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE32" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH32" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI32" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO32" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP32" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW32" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX32" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY32" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE32" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914511, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF32" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>9.712984233453664e-06</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_no_fragmentation_smotenc_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LGBMClassifier', 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 10, 'sampling_strategy': 0.86}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9160886104273886</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.9227272727272727</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.9541284403669724</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>0.4369640350341797, 0.5162317752838135, 0.5495171546936035, 0.5638258457183838, 0.5647039413452148, 0.4504101276397705, 0.5306270122528076</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.5160399845668248</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.5306270122528076</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.04861729881749643</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>0.008296966552734375, 0.0077440738677978516, 0.00766301155090332, 0.008063077926635742, 0.010455131530761719, 0.008137941360473633, 0.00763392448425293</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.008284875324794225</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.008063077926635742</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.0009168158904602554</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.8301886792452831, 0.9245283018867925, 0.8490566037735849, 0.9622641509433962, 0.9245283018867925, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>0.8076923076923077, 0.8159340659340659, 0.88003663003663, 0.8287545787545787, 0.9514652014652014, 0.9029304029304028, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.8732339089481946</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.88003663003663</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.05260555971040238</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.8979235299990017</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.04471867659679967</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>0.7407407407407408, 0.7096774193548386, 0.8461538461538461, 0.7333333333333334, 0.9285714285714286, 0.8571428571428571, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>0.9135802469135802, 0.8799999999999999, 0.9500000000000001, 0.8947368421052632, 0.9743589743589743, 0.9487179487179487, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.9298232047354855</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.03169637667534765</v>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>0.8271604938271605, 0.7948387096774192, 0.8980769230769231, 0.8140350877192983, 0.9514652014652014, 0.9029304029304028, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU33" t="n">
+        <v>0.8707891946508648</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.8980769230769231</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.05410539596946609</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.8117551845662444</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0.07701347062511781</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.6470588235294118, 0.9166666666666666, 0.6875, 0.9285714285714286, 0.8571428571428571, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9166666666666666, 0.926829268292683, 0.918918918918919, 0.9743589743589743, 0.9487179487179487, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.9342024472686493</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0.03107002065544107</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0.8118247298919566</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0.09981616988290638</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.9285714285714286, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8461538461538461, 0.9743589743589743, 0.8717948717948718, 0.9743589743589743, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK33" t="n">
+        <v>0.9267399267399268</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0.04633373861052569</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0.8197278911564626</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0.08618271741033966</v>
+      </c>
+      <c r="BQ33" t="inlineStr">
+        <is>
+          <t>0.9675213675213675, 0.9102564102564102, 0.9816849816849818, 0.9432234432234432, 0.9798534798534799, 0.9175824175824177, 0.9853479853479854</t>
+        </is>
+      </c>
+      <c r="BR33" t="n">
+        <v>0.9550671550671551</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0.9675213675213675</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0.02915056624211423</v>
+      </c>
+      <c r="BU33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
